--- a/meta/1-b-1-1.xlsx
+++ b/meta/1-b-1-1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Лист" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="144525"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -103,18 +104,6 @@
     <t>1.b.1.1 Доля текущих и капитальных государственных расходов в секторах</t>
   </si>
   <si>
-    <t>Министерство финансов Кыргызской Республики (Управление бюджетной политики)</t>
-  </si>
-  <si>
-    <t>Омурова Т.А.</t>
-  </si>
-  <si>
-    <t>t.omurova@minfin.kg</t>
-  </si>
-  <si>
-    <t>+996-0312-62-53-13 (доб 1110, 1112)</t>
-  </si>
-  <si>
     <t>Текущие и капитальные государственные расходы в секторах (экономические вопросы, здравоохранение, образование и жилищно-коммунальные услуги) в общей сумме государственных расходов в этих секторах. Затраты, связанные с осуществлением государством своих функций.</t>
   </si>
   <si>
@@ -147,6 +136,18 @@
   <si>
     <t>МФ КР: www.minfin.kg;
 НСК: www.stat.gov.kg</t>
+  </si>
+  <si>
+    <t>Министерство финансов Кыргызской Республики (Центральное казначейство, Отдел консолидации отчетов)</t>
+  </si>
+  <si>
+    <t>m.kasymkulova@minfin.kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +996-0312-62-04-16 (доб. 3440)</t>
+  </si>
+  <si>
+    <t>Касымкулова М.К.</t>
   </si>
 </sst>
 </file>
@@ -159,14 +160,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -191,6 +184,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -233,30 +233,33 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -269,9 +272,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -320,7 +320,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -355,7 +355,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -607,14 +607,14 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -622,7 +622,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -630,37 +630,37 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>32</v>
+      <c r="B9" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>42</v>
+      <c r="B10" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="7"/>
     </row>
     <row r="12" spans="1:2" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -668,7 +668,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -681,14 +681,14 @@
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="7"/>
     </row>
     <row r="16" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -696,21 +696,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="7"/>
     </row>
     <row r="19" spans="1:2" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -729,14 +729,14 @@
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2"/>
+      <c r="B22" s="7"/>
     </row>
     <row r="23" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -744,7 +744,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -752,7 +752,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -760,7 +760,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
